--- a/khurana_cv/data/training.xlsx
+++ b/khurana_cv/data/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\havis\University of Oregon Dropbox\Havi Khurana\Personal\Coding projects\khurana_cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8743519F-B905-44F4-BCE5-4A7FC0202CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA5FB1B-5C7D-449D-9852-54C18E568F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
   <si>
     <t>name</t>
   </si>
@@ -198,6 +198,12 @@
   </si>
   <si>
     <t>US Department of Education and American Institutes for Research</t>
+  </si>
+  <si>
+    <t>State School Finance Workshop Series</t>
+  </si>
+  <si>
+    <t>EdFund</t>
   </si>
 </sst>
 </file>
@@ -548,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.7265625" customWidth="1"/>
@@ -794,6 +800,26 @@
         <v>44</v>
       </c>
     </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="1">
+        <v>45665</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46132</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
